--- a/laporan_padel_dki_jakarta_2026-10-10.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-10.xlsx
@@ -4470,16 +4470,16 @@
         <v>32</v>
       </c>
       <c r="D32" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.025.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp814.000</t>
+          <t>Rp887.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.352.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp675.000</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp200.000</t>
+          <t>Rp125.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -6711,16 +6711,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.128.000</t>
+          <t>Rp7.209.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.320.000</t>
+          <t>Rp9.590.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.720.000</t>
+          <t>Rp2.890.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-10.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-10.xlsx
@@ -544,16 +544,16 @@
         <v>168</v>
       </c>
       <c r="D4" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp18.780.000</t>
+          <t>Rp19.380.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.335.000</t>
+          <t>Rp3.659.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.490.000</t>
+          <t>Rp1.639.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>126</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp17.204.000</t>
+          <t>Rp17.534.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp3.700.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.140.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.040.000</t>
+          <t>Rp4.160.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.840.000</t>
+          <t>Rp3.465.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.890.000</t>
+          <t>Rp2.430.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>18</v>
       </c>
       <c r="D55" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp447.000</t>
+          <t>Rp596.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp5.625.000</t>
+          <t>Rp5.175.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>85</v>
       </c>
       <c r="D60" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp1.341.000</t>
+          <t>Rp1.192.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2404,16 +2404,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp225.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>26</v>
       </c>
       <c r="D65" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.554.000</t>
+          <t>Rp3.663.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp2.030.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp8.265.000</t>
+          <t>Rp8.460.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp3.415.000</t>
+          <t>Rp3.290.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp13.226.000</t>
+          <t>Rp17.116.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.842.000</t>
+          <t>Rp1.967.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.994.000</t>
+          <t>Rp4.194.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp9.150.000</t>
+          <t>Rp8.800.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp297.000</t>
+          <t>Rp249.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp75.000 - Rp99.000</t>
         </is>
       </c>
     </row>
@@ -4501,16 +4501,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.425.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>75</v>
       </c>
       <c r="D35" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp6.340.000</t>
+          <t>Rp6.470.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.925.000</t>
+          <t>Rp6.175.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp5.130.000</t>
+          <t>Rp5.670.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp40.850.000</t>
+          <t>Rp42.700.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.546.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.210.000</t>
+          <t>Rp4.485.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp376.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>82</v>
       </c>
       <c r="D4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.200.000</t>
+          <t>Rp10.480.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp198.000</t>
+          <t>Rp267.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.632.000</t>
+          <t>Rp2.820.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp7.725.000</t>
+          <t>Rp7.900.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp792.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.100.000</t>
+          <t>Rp18.500.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.209.000</t>
+          <t>Rp7.371.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>96</v>
       </c>
       <c r="D29" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp5.640.000</t>
+          <t>Rp6.440.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp6.097.000</t>
+          <t>Rp6.251.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp3.875.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp18.350.000</t>
+          <t>Rp18.450.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.512.000</t>
+          <t>Rp4.888.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>180</v>
       </c>
       <c r="D37" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp6.650.000</t>
+          <t>Rp6.825.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>34</v>
       </c>
       <c r="D38" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp188.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>112</v>
       </c>
       <c r="D44" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp10.400.000</t>
+          <t>Rp10.850.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>108</v>
       </c>
       <c r="D48" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D50" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.310.000</t>
+          <t>Rp14.550.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.225.000</t>
+          <t>Rp6.420.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp150.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp3.020.000</t>
+          <t>Rp4.010.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.599.982</t>
+          <t>Rp4.399.978</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>36</v>
       </c>
       <c r="D36" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.955.000</t>
+          <t>Rp5.465.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.670.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-10.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-10.xlsx
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp14.100.000</t>
+          <t>Rp14.430.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.639.000</t>
+          <t>Rp2.235.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>126</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp17.534.000</t>
+          <t>Rp17.814.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.740.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.530.000</t>
+          <t>Rp4.730.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.838.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.277.000</t>
+          <t>Rp3.057.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp6.172.000</t>
+          <t>Rp6.570.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>36</v>
       </c>
       <c r="D54" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp5.175.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp3.439.000</t>
+          <t>Rp3.757.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp9.873.000</t>
+          <t>Rp10.671.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.663.000</t>
+          <t>Rp3.861.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>68</v>
       </c>
       <c r="D71" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.160.000</t>
+          <t>Rp1.460.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp1.683.000</t>
+          <t>Rp1.881.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>135</v>
       </c>
       <c r="D84" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.475.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp7.970.000</t>
+          <t>Rp8.470.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.863.000</t>
+          <t>Rp1.944.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>133</v>
       </c>
       <c r="D3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp18.591.000</t>
+          <t>Rp18.767.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp17.116.000</t>
+          <t>Rp19.450.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp4.900.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.194.000</t>
+          <t>Rp4.794.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.125.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>24</v>
       </c>
       <c r="D39" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>77</v>
       </c>
       <c r="D44" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp14.300.000</t>
+          <t>Rp15.650.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp425.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp6.175.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>84</v>
       </c>
       <c r="D67" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.100.000</t>
+          <t>Rp8.300.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp10.550.000</t>
+          <t>Rp11.840.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>82</v>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.480.000</t>
+          <t>Rp10.555.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp267.000</t>
+          <t>Rp633.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.875.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp7.900.000</t>
+          <t>Rp8.075.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.371.000</t>
+          <t>Rp7.857.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>48</v>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp198.000</t>
+          <t>Rp678.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.420.000</t>
+          <t>Rp4.760.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>96</v>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp6.440.000</t>
+          <t>Rp6.620.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.875.000</t>
+          <t>Rp4.375.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp18.450.000</t>
+          <t>Rp18.600.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>14</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>170</v>
       </c>
       <c r="D40" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp22.752.000</t>
+          <t>Rp23.051.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>80</v>
       </c>
       <c r="D42" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.625.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>112</v>
       </c>
       <c r="D44" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp10.850.000</t>
+          <t>Rp10.975.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>108</v>
       </c>
       <c r="D48" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.550.000</t>
+          <t>Rp15.050.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.887.000</t>
+          <t>Rp3.289.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.420.000</t>
+          <t>Rp6.270.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.880.000</t>
+          <t>Rp16.960.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp11.760.000</t>
+          <t>Rp11.970.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.399.978</t>
+          <t>Rp4.799.976</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp7.500.000</t>
+          <t>Rp7.800.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>45</v>
       </c>
       <c r="D30" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.925.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.695.000</t>
+          <t>Rp3.430.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>72</v>
       </c>
       <c r="D42" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.620.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-10.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-10.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.810.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp340.000</t>
+          <t>Rp150.000 - Rp340.000</t>
         </is>
       </c>
     </row>
@@ -544,16 +544,16 @@
         <v>168</v>
       </c>
       <c r="D4" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp19.380.000</t>
+          <t>Rp19.680.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp880.000</t>
+          <t>Rp1.144.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>126</v>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp17.814.000</t>
+          <t>Rp18.222.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp3.725.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.380.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.730.000</t>
+          <t>Rp5.150.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1068,14 +1068,14 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D21" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp305.000</t>
+          <t>Rp75.000 - Rp305.000</t>
         </is>
       </c>
     </row>
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp14.996.000</t>
+          <t>Rp16.541.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp4.450.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.131.000</t>
+          <t>Rp3.171.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.483.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.434.000</t>
+          <t>Rp3.582.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.465.000</t>
+          <t>Rp4.035.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.580.000</t>
+          <t>Rp4.296.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.057.000</t>
+          <t>Rp5.787.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.430.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp630.000</t>
+          <t>Rp840.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.625.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp198.000</t>
+          <t>Rp446.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp3.757.000</t>
+          <t>Rp3.857.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.301.000</t>
+          <t>Rp1.981.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp10.671.000</t>
+          <t>Rp11.468.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.079.000</t>
+          <t>Rp2.376.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.861.000</t>
+          <t>Rp4.158.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.520.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>45</v>
       </c>
       <c r="D76" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.875.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp1.881.000</t>
+          <t>Rp2.277.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>36</v>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>108</v>
       </c>
       <c r="D85" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>90</v>
       </c>
       <c r="D89" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp1.920.000</t>
+          <t>Rp2.640.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp3.290.000</t>
+          <t>Rp4.010.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp8.470.000</t>
+          <t>Rp8.710.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.944.000</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>133</v>
       </c>
       <c r="D3" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp18.767.000</t>
+          <t>Rp19.295.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp19.450.000</t>
+          <t>Rp22.562.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp6.650.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.794.000</t>
+          <t>Rp4.894.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp8.800.000</t>
+          <t>Rp9.250.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.455.000</t>
+          <t>Rp5.670.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.380.000</t>
+          <t>Rp1.640.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp380.000</t>
+          <t>Rp510.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp5.825.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>75</v>
       </c>
       <c r="D35" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp6.470.000</t>
+          <t>Rp6.970.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp29.600.000</t>
+          <t>Rp30.450.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp7.500.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp8.075.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.582.000</t>
+          <t>Rp4.378.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp11.200.000</t>
+          <t>Rp10.850.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp887.000</t>
+          <t>Rp960.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.380.000</t>
+          <t>Rp1.620.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp5.670.000</t>
+          <t>Rp6.210.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>84</v>
       </c>
       <c r="D67" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp8.300.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>162</v>
       </c>
       <c r="D70" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp8.300.000</t>
+          <t>Rp8.650.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>313</v>
+        <v>269</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp12.320.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.920.000</t>
+          <t>Rp2.240.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp42.700.000</t>
+          <t>Rp43.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.650.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.368.000</t>
+          <t>Rp4.686.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp650.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp11.840.000</t>
+          <t>Rp12.680.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>82</v>
       </c>
       <c r="D4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.555.000</t>
+          <t>Rp10.835.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp633.000</t>
+          <t>Rp970.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.000.000</t>
+          <t>Rp9.250.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp20.175.000</t>
+          <t>Rp20.345.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.820.000</t>
+          <t>Rp3.572.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp8.075.000</t>
+          <t>Rp8.600.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.492.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp792.000</t>
+          <t>Rp1.089.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.500.000</t>
+          <t>Rp18.900.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7052,21 +7052,21 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.857.000</t>
+          <t>Rp7.948.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rp81.000</t>
+          <t>Rp10.000 - Rp81.000</t>
         </is>
       </c>
     </row>
@@ -7083,16 +7083,16 @@
         <v>48</v>
       </c>
       <c r="D24" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp678.000</t>
+          <t>Rp1.158.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.760.000</t>
+          <t>Rp5.610.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp6.251.000</t>
+          <t>Rp7.059.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp4.625.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp18.600.000</t>
+          <t>Rp19.050.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>14</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>170</v>
       </c>
       <c r="D40" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp23.051.000</t>
+          <t>Rp23.649.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>128</v>
       </c>
       <c r="D41" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp5.980.000</t>
+          <t>Rp7.176.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>112</v>
       </c>
       <c r="D44" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp10.975.000</t>
+          <t>Rp11.425.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>102</v>
       </c>
       <c r="D46" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>36</v>
       </c>
       <c r="D47" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>102</v>
       </c>
       <c r="D49" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D50" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.175.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>90</v>
       </c>
       <c r="D51" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.050.000</t>
+          <t>Rp15.550.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.289.000</t>
+          <t>Rp1.794.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp820.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.560.000</t>
+          <t>Rp1.820.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.590.000</t>
+          <t>Rp10.630.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.772.000</t>
+          <t>Rp2.887.500</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.010.000</t>
+          <t>Rp5.795.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp16.960.000</t>
+          <t>Rp17.760.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.425.000</t>
+          <t>Rp1.644.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.799.976</t>
+          <t>Rp4.999.975</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>45</v>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.925.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.430.000</t>
+          <t>Rp4.145.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>112</v>
       </c>
       <c r="D37" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.080.000</t>
+          <t>Rp2.640.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>51</v>
       </c>
       <c r="D38" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.665.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.670.000</t>
+          <t>Rp5.940.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.704.000</t>
+          <t>Rp3.887.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>68</v>
       </c>
       <c r="D43" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.620.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-10.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-10.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.020.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>126</v>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp18.222.000</t>
+          <t>Rp18.424.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.160.000</t>
+          <t>Rp4.320.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.582.000</t>
+          <t>Rp3.778.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.430.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.981.000</t>
+          <t>Rp2.141.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.158.000</t>
+          <t>Rp4.356.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.875.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.277.000</t>
+          <t>Rp2.376.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.650.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp960.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.050.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp970.000</t>
+          <t>Rp1.644.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.900.000</t>
+          <t>Rp20.300.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.948.000</t>
+          <t>Rp8.110.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp5.610.000</t>
+          <t>Rp5.780.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp19.050.000</t>
+          <t>Rp19.150.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>180</v>
       </c>
       <c r="D37" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp6.825.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>170</v>
       </c>
       <c r="D40" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp23.649.000</t>
+          <t>Rp23.948.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp954.000</t>
+          <t>Rp1.272.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.550.000</t>
+          <t>Rp15.660.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>34</v>
       </c>
       <c r="D34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.825.000</t>
+          <t>Rp3.075.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.940.000</t>
+          <t>Rp6.075.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
